--- a/data/LOZANO MOLINA TITO.xlsx
+++ b/data/LOZANO MOLINA TITO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+          <t>VERA ARCE MARIA ISABEL</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1099,144 +1099,84 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LOZANO MOLINA TITO</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>VERA ARCE MARIA ISABEL</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="R12" s="4" t="inlineStr">
-        <is>
-          <t>0 de 10</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>0 de 9</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1470,7 +1410,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -1497,7 +1437,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -1524,7 +1464,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+          <t>VERA ARCE MARIA ISABEL</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1544,46 +1484,19 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LOZANO MOLINA TITO</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>VERA ARCE MARIA ISABEL</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="6" t="n">
+      <c r="C11" s="6" t="n">
         <v>633.6</v>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6" t="n">
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/LOZANO MOLINA TITO.xlsx
+++ b/data/LOZANO MOLINA TITO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARBIZACONSTRUC S.A.</t>
+          <t>DELGADO COPPIANO JORGE RODOLFO</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DELGADO COPPIANO JORGE RODOLFO</t>
+          <t>DELGADO LOOR JORGE ARTURO</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DELGADO LOOR JORGE ARTURO</t>
+          <t>DISALME CIA. LTDA.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DISALME CIA. LTDA.</t>
+          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
+          <t>VERA ARCE MARIA ISABEL</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -859,324 +859,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LOZANO MOLINA TITO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LOZANO MOLINA TITO</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LOZANO MOLINA TITO</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LOZANO MOLINA TITO</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>VERA ARCE MARIA ISABEL</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="Q11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
-        </is>
-      </c>
-      <c r="R11" s="4" t="inlineStr">
-        <is>
-          <t>0 de 9</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
         </is>
       </c>
     </row>
@@ -1191,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1248,11 +1008,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARBIZACONSTRUC S.A.</t>
+          <t>DELGADO COPPIANO JORGE RODOLFO</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>633.6</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
@@ -1275,7 +1035,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DELGADO COPPIANO JORGE RODOLFO</t>
+          <t>DELGADO LOOR JORGE ARTURO</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -1302,7 +1062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DELGADO LOOR JORGE ARTURO</t>
+          <t>DISALME CIA. LTDA.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -1329,7 +1089,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DISALME CIA. LTDA.</t>
+          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -1356,7 +1116,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
+          <t>VERA ARCE MARIA ISABEL</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -1376,127 +1136,19 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LOZANO MOLINA TITO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LOZANO MOLINA TITO</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LOZANO MOLINA TITO</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LOZANO MOLINA TITO</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>VERA ARCE MARIA ISABEL</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" s="6" t="n">
-        <v>633.6</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6" t="n">
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>0</v>
       </c>
     </row>
